--- a/九龙-九龙塘-The Monet 第3期/The Monet 第3期_销控明细表.xlsx
+++ b/九龙-九龙塘-The Monet 第3期/The Monet 第3期_销控明细表.xlsx
@@ -17,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
-  <fonts count="19">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,11 +117,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,9 +203,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,9 +248,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -640,8 +627,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -829,16 +816,18 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>119900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -971,16 +960,18 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>70700000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
@@ -1113,16 +1104,18 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>97900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1255,16 +1248,18 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>105000000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1397,16 +1392,18 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>70000000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -1539,16 +1536,18 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>96900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -1681,16 +1680,18 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>102900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -1823,16 +1824,18 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>68700000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -1965,16 +1968,18 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>95100000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2107,16 +2112,18 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>101900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -2249,16 +2256,18 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>68000000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -2391,16 +2400,18 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>94100000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -2533,16 +2544,18 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>100900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -2675,16 +2688,18 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>67300000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -2817,16 +2832,18 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>93200000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -2959,16 +2976,18 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>99900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
@@ -3101,16 +3120,18 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>66600000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
@@ -3243,16 +3264,18 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>92300000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
@@ -3385,16 +3408,18 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>98400000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -3527,16 +3552,18 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>65600000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
@@ -3669,16 +3696,18 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>90900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
@@ -3811,16 +3840,18 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>95200000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
@@ -3953,16 +3984,18 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>93900000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
@@ -4020,105 +4053,105 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>23</t>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4126,15 +4159,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$11990万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4144,20 +4177,20 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9790万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4165,22 +4198,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$7070万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4188,15 +4221,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$10500万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4206,20 +4239,20 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9690万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4227,22 +4260,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$7000万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4250,15 +4283,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$10290万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4268,20 +4301,20 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9510万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4289,22 +4322,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$6870万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4312,15 +4345,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$10190万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4330,20 +4363,20 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9410万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4351,22 +4384,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$6800万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4374,15 +4407,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$10090万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4392,20 +4425,20 @@
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9320万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4413,22 +4446,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$6730万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4436,15 +4469,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$9990万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4454,20 +4487,20 @@
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9230万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4475,22 +4508,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$6660万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4498,15 +4531,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$9840万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4516,20 +4549,20 @@
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9090万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
 -
@@ -4537,22 +4570,22 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
-$6560万
--
-(25年-05月-09日)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
 -
@@ -4560,15 +4593,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>B | 0呎 (null房)
-$9520万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>C | 0呎 (null房)
 -
@@ -4578,21 +4611,21 @@
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>A | 0呎 (null房)
-$9390万
--
-(25年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr"/>
-      <c r="D20" s="21" t="inlineStr"/>
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr"/>
+      <c r="D20" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
